--- a/selenium/selenium_test_results.xlsx
+++ b/selenium/selenium_test_results.xlsx
@@ -419,7 +419,7 @@
         <v>Execution Date</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>TC-LOGIN-001</v>
       </c>
@@ -429,14 +429,16 @@
       <c r="C2" t="str">
         <v>User successfully logs in using Google and is redirected to Swap-and-Share</v>
       </c>
-      <c r="D2" t="str">
-        <v>Test failed: Cannot read properties of null (reading 'startsWith')</v>
+      <c r="D2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Test failed: invalid session id: session deleted as the browser has closed the connection
+from disconnected: not connected to DevTools
+  (Session info: chrome=153.0.8010.47)</v>
       </c>
       <c r="E2" t="str">
         <v>FAIL</v>
       </c>
       <c r="F2" t="str">
-        <v>9/23/2026, 12:27:51 PM</v>
+        <v>9/28/2026, 12:34:56 PM</v>
       </c>
     </row>
   </sheetData>

--- a/selenium/selenium_test_results.xlsx
+++ b/selenium/selenium_test_results.xlsx
@@ -419,7 +419,7 @@
         <v>Execution Date</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
         <v>TC-LOGIN-001</v>
       </c>
@@ -429,16 +429,14 @@
       <c r="C2" t="str">
         <v>User successfully logs in using Google and is redirected to Swap-and-Share</v>
       </c>
-      <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Test failed: invalid session id: session deleted as the browser has closed the connection
-from disconnected: not connected to DevTools
-  (Session info: chrome=153.0.8010.47)</v>
+      <c r="D2" t="str">
+        <v>Test failed: Wait timed out after 15098ms</v>
       </c>
       <c r="E2" t="str">
         <v>FAIL</v>
       </c>
       <c r="F2" t="str">
-        <v>9/28/2026, 12:34:56 PM</v>
+        <v>9/28/2026, 1:19:39 PM</v>
       </c>
     </row>
   </sheetData>

--- a/selenium/selenium_test_results.xlsx
+++ b/selenium/selenium_test_results.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,51 +399,177 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="1" t="str">
         <v>Test Case ID</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="1" t="str">
         <v>Test Scenario</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" s="1" t="str">
         <v>Expected Result</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" s="1" t="str">
         <v>Actual Result</v>
       </c>
-      <c r="E1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="E1" s="1" t="str">
         <v>Execution Date</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
+    <row r="2" xml:space="preserve">
+      <c r="A2" s="1" t="str">
         <v>TC-LOGIN-001</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" s="1" t="str">
         <v>Google OAuth Login</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="1" t="str">
         <v>User successfully logs in using Google and is redirected to Swap-and-Share</v>
       </c>
-      <c r="D2" t="str">
-        <v>Test failed: Wait timed out after 15098ms</v>
-      </c>
-      <c r="E2" t="str">
+      <c r="D2" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Test failed: Timed out: neither the Google page nor a redirect back to the app appeared after clicking sign-in
+Wait timed out after 30056ms</v>
+      </c>
+      <c r="E2" s="1" t="str">
         <v>FAIL</v>
       </c>
-      <c r="F2" t="str">
-        <v>9/28/2026, 1:19:39 PM</v>
+      <c r="F2" s="1" t="str">
+        <v>9/30/2026, 1:36:39 AM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="str">
+        <v>TC-LOGOUT-001</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>Authenticated user logout</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>User should be logged out, redirected to Home, and shown the Login option.</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <v>Test failed: Login link not displayed after logout. POST /auth/logout -&gt; no response (request hung, was blocked, or never sent); server session GET /auth/user -&gt; 200.</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <v>9/30/2026, 1:37:05 AM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="str">
+        <v>TC-LOGOUT-002</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <v>Verify session invalidation after logout</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>Authenticated session should be destroyed and /auth/user should reject the request with 401.</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <v>Skipped: TC-LOGOUT-001 failed</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <v>SKIPPED</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <v>9/30/2026, 1:37:05 AM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="str">
+        <v>TC-LOGIN-002</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <v>Navbar reflects logged-in state</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <v>After login the navbar shows the Logout button and hides the Login link.</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <v>Skipped: TC-LOGIN-001 failed</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <v>SKIPPED</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <v>9/30/2026, 1:36:39 AM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="str">
+        <v>TC-LOGIN-003</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <v>Session persists after page reload</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <v>After reloading the page the user is still logged in.</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <v>Skipped: TC-LOGIN-001 failed</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <v>SKIPPED</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <v>9/30/2026, 1:36:39 AM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="str">
+        <v>TC-LOGOUT-003</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <v>Protected API rejects request after logout</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <v>/api/cart should return 401 'Please log in first' once the session is destroyed.</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <v>Skipped: TC-LOGOUT-001 failed</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <v>SKIPPED</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <v>9/30/2026, 1:37:05 AM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="str">
+        <v>TC-LOGOUT-004</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <v>Logged-out state persists after page reload</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <v>After reloading Home the Login link is shown and the Logout button is absent.</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <v>Skipped: TC-LOGOUT-001 failed</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <v>SKIPPED</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <v>9/30/2026, 1:37:05 AM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/selenium/selenium_test_results.xlsx
+++ b/selenium/selenium_test_results.xlsx
@@ -399,15 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="70.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:F21"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -426,7 +418,7 @@
         <v>Execution Date</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" s="1" t="str">
         <v>TC-LOGIN-001</v>
       </c>
@@ -436,15 +428,14 @@
       <c r="C2" s="1" t="str">
         <v>User successfully logs in using Google and is redirected to Swap-and-Share</v>
       </c>
-      <c r="D2" s="1" t="str" xml:space="preserve">
-        <v xml:space="preserve">Test failed: Timed out: neither the Google page nor a redirect back to the app appeared after clicking sign-in
-Wait timed out after 30056ms</v>
+      <c r="D2" s="1" t="str">
+        <v>Google authentication successful. First Google account was selected, user was redirected to Swap-and-Share, and /auth/user returned authenticated user data.</v>
       </c>
       <c r="E2" s="1" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="F2" s="1" t="str">
-        <v>9/30/2026, 1:36:39 AM</v>
+        <v>9/30/2026, 12:11:38 PM</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +449,13 @@
         <v>User should be logged out, redirected to Home, and shown the Login option.</v>
       </c>
       <c r="D3" s="1" t="str">
-        <v>Test failed: Login link not displayed after logout. POST /auth/logout -&gt; no response (request hung, was blocked, or never sent); server session GET /auth/user -&gt; 200.</v>
+        <v>User successfully logged out, was redirected to Home, and the Login option was displayed.</v>
       </c>
       <c r="E3" s="1" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="F3" s="1" t="str">
-        <v>9/30/2026, 1:37:05 AM</v>
+        <v>9/30/2026, 12:12:43 PM</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +469,13 @@
         <v>Authenticated session should be destroyed and /auth/user should reject the request with 401.</v>
       </c>
       <c r="D4" s="1" t="str">
-        <v>Skipped: TC-LOGOUT-001 failed</v>
+        <v>Logout destroyed the session. /auth/user returned 401 {"error":"Not authenticated"}.</v>
       </c>
       <c r="E4" s="1" t="str">
-        <v>SKIPPED</v>
+        <v>PASS</v>
       </c>
       <c r="F4" s="1" t="str">
-        <v>9/30/2026, 1:37:05 AM</v>
+        <v>9/30/2026, 12:12:43 PM</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +489,13 @@
         <v>After login the navbar shows the Logout button and hides the Login link.</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>Skipped: TC-LOGIN-001 failed</v>
+        <v>Logout button is displayed and the Login link is hidden after login.</v>
       </c>
       <c r="E5" s="1" t="str">
-        <v>SKIPPED</v>
+        <v>PASS</v>
       </c>
       <c r="F5" s="1" t="str">
-        <v>9/30/2026, 1:36:39 AM</v>
+        <v>9/30/2026, 12:11:38 PM</v>
       </c>
     </row>
     <row r="6">
@@ -518,13 +509,13 @@
         <v>After reloading the page the user is still logged in.</v>
       </c>
       <c r="D6" s="1" t="str">
-        <v>Skipped: TC-LOGIN-001 failed</v>
+        <v>User remained logged in after reload; Logout button shown and /auth/user returned 200.</v>
       </c>
       <c r="E6" s="1" t="str">
-        <v>SKIPPED</v>
+        <v>PASS</v>
       </c>
       <c r="F6" s="1" t="str">
-        <v>9/30/2026, 1:36:39 AM</v>
+        <v>9/30/2026, 12:11:39 PM</v>
       </c>
     </row>
     <row r="7">
@@ -538,13 +529,13 @@
         <v>/api/cart should return 401 'Please log in first' once the session is destroyed.</v>
       </c>
       <c r="D7" s="1" t="str">
-        <v>Skipped: TC-LOGOUT-001 failed</v>
+        <v>/api/cart rejected the request with 401 {"error":"Please log in first"}.</v>
       </c>
       <c r="E7" s="1" t="str">
-        <v>SKIPPED</v>
+        <v>PASS</v>
       </c>
       <c r="F7" s="1" t="str">
-        <v>9/30/2026, 1:37:05 AM</v>
+        <v>9/30/2026, 12:12:43 PM</v>
       </c>
     </row>
     <row r="8">
@@ -558,18 +549,281 @@
         <v>After reloading Home the Login link is shown and the Logout button is absent.</v>
       </c>
       <c r="D8" s="1" t="str">
-        <v>Skipped: TC-LOGOUT-001 failed</v>
+        <v>Login link displayed and Logout button absent after reload; user stayed logged out.</v>
       </c>
       <c r="E8" s="1" t="str">
-        <v>SKIPPED</v>
+        <v>PASS</v>
       </c>
       <c r="F8" s="1" t="str">
-        <v>9/30/2026, 1:37:05 AM</v>
+        <v>9/30/2026, 12:12:44 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="str">
+        <v>TC-NAV-001</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <v>Home page navigation</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <v>User should be redirected to the Swap-and-Share Home page.</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <v>Home page successfully loaded at http://localhost:5173/.</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <v>9/30/2026, 11:46:01 AM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="str">
+        <v>TC-NAV-002</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <v>Inventory navigation</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <v>Clicking Inventory should navigate the user to the Shop page.</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <v>Inventory page successfully opened at http://localhost:5173/shop.</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <v>9/30/2026, 11:46:01 AM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="str">
+        <v>TC-NAV-003</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <v>Sell/Donate navigation</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <v>Clicking Sell/Donate should navigate the user to the listing page.</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <v>Sell/Donate page successfully opened at http://localhost:5173/login.</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <v>9/30/2026, 11:46:02 AM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="str">
+        <v>TC-NAV-004</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <v>My Listings navigation</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <v>Clicking My Listings should open the user's listings page.</v>
+      </c>
+      <c r="D12" s="1" t="str">
+        <v>My Listings page successfully opened at http://localhost:5173/my-listings.</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <v>9/30/2026, 11:46:03 AM</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" s="1" t="str">
+        <v>TC-NAV-ERROR</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <v>Navigation test execution</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <v>All navigation test cases should execute successfully.</v>
+      </c>
+      <c r="D13" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Test execution failed: Waiting for element to be located By(xpath, //a[contains(normalize-space(), 'Cart')])
+Wait timed out after 10120ms</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <v>9/30/2026, 11:46:13 AM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="str">
+        <v>TC-NAV-001</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <v>Home page navigation</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <v>User should be redirected to the Swap-and-Share Home page.</v>
+      </c>
+      <c r="D14" s="1" t="str">
+        <v>Home page successfully loaded at http://localhost:5173/.</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F14" s="1" t="str">
+        <v>9/30/2026, 11:48:47 AM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="str">
+        <v>TC-NAV-ERROR</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <v>Navigation test execution</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <v>All navigation test cases should execute successfully.</v>
+      </c>
+      <c r="D15" s="1" t="str">
+        <v>Test execution failed: Wait timed out after 10200ms</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F15" s="1" t="str">
+        <v>9/30/2026, 11:48:57 AM</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="str">
+        <v>TC-NAV-001</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <v>Home page navigation</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <v>User should be redirected to the Swap-and-Share Home page.</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <v>Home page successfully loaded at http://localhost:5173/.</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F16" s="1" t="str">
+        <v>9/30/2026, 11:50:38 AM</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" s="1" t="str">
+        <v>TC-NAV-ERROR</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <v>Navigation test execution</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <v>All navigation test cases should execute successfully.</v>
+      </c>
+      <c r="D17" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Test execution failed: element not interactable
+  (Session info: chrome=151.0.7922.176)</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <v>9/30/2026, 11:50:38 AM</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="str">
+        <v>TC-NAV-001</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <v>Home page navigation</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <v>User should be redirected to the Swap-and-Share Home page.</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <v>Home page successfully loaded at http://localhost:5173/.</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F18" s="1" t="str">
+        <v>9/30/2026, 11:51:04 AM</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" s="1" t="str">
+        <v>TC-NAV-ERROR</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <v>Navigation test execution</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <v>All navigation test cases should execute successfully.</v>
+      </c>
+      <c r="D19" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Test execution failed: element not interactable
+  (Session info: chrome=151.0.7922.176)</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F19" s="1" t="str">
+        <v>9/30/2026, 11:51:04 AM</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="str">
+        <v>TC-NAV-001</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <v>Home page navigation</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <v>User should be redirected to the Swap-and-Share Home page.</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <v>Home page successfully loaded at http://localhost:5173/.</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F20" s="1" t="str">
+        <v>9/30/2026, 12:14:14 PM</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="str">
+        <v>TC-NAV-ERROR</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <v>Navigation test execution</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <v>All navigation test cases should execute successfully.</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <v>Test execution failed: Wait timed out after 10078ms</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F21" s="1" t="str">
+        <v>9/30/2026, 12:14:24 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/selenium/selenium_test_results.xlsx
+++ b/selenium/selenium_test_results.xlsx
@@ -399,7 +399,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -821,9 +829,51 @@
         <v>9/30/2026, 12:14:24 PM</v>
       </c>
     </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" s="1" t="str">
+        <v>TC-PRODUCT-001</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <v>Product inventory loads</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <v>Products should be displayed on the Shop/Inventory page.</v>
+      </c>
+      <c r="D22" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Test failed: No product cards were displayed on the Shop page.
+Wait timed out after 10171ms</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F22" s="1" t="str">
+        <v>9/30/2026, 12:22:23 PM</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" s="1" t="str">
+        <v>TC-PRODUCT-002</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <v>Product information is displayed</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <v>Each displayed product should contain product information such as name and price.</v>
+      </c>
+      <c r="D23" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Test failed: No product cards were displayed.
+Wait timed out after 10148ms</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="F23" s="1" t="str">
+        <v>9/30/2026, 12:22:33 PM</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F23"/>
   </ignoredErrors>
 </worksheet>
 </file>